--- a/data/bulk-upload-points/upload-points-missing-fields.xlsx
+++ b/data/bulk-upload-points/upload-points-missing-fields.xlsx
@@ -1,21 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{862AA192-75D9-4338-A974-516F74448913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cabe-1078\Desktop\Noted_CAB_2026\Data_Test_WUPoint\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E252F579-11A1-444D-B358-838AF2104FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="data" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+  <si>
+    <t>cifId</t>
+  </si>
+  <si>
+    <t>firstName</t>
+  </si>
   <si>
     <t>remark:</t>
   </si>
@@ -23,33 +39,33 @@
     <t>service</t>
   </si>
   <si>
-    <t>TRANSFER_MONEY</t>
-  </si>
-  <si>
-    <t>RECEIVE_MONEY</t>
+    <t>Transfer Money</t>
+  </si>
+  <si>
+    <t>Receive Money</t>
   </si>
   <si>
     <t>channel</t>
   </si>
   <si>
-    <t>MOBILE_BANKING</t>
-  </si>
-  <si>
-    <t>BRANCH</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>cifId</t>
-  </si>
-  <si>
-    <t>phoneNumber</t>
+    <t>Mobile Banking</t>
+  </si>
+  <si>
+    <t>Branch</t>
   </si>
   <si>
     <t>idType</t>
   </si>
   <si>
+    <t>PASSPORT</t>
+  </si>
+  <si>
+    <t>NID</t>
+  </si>
+  <si>
+    <t>lastName</t>
+  </si>
+  <si>
     <t>idNumber</t>
   </si>
   <si>
@@ -68,23 +84,29 @@
     <t>description</t>
   </si>
   <si>
+    <t>9999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veayor </t>
+  </si>
+  <si>
     <t>USD</t>
   </si>
   <si>
-    <t>PASSPORT</t>
-  </si>
-  <si>
-    <t>Earn from purchase</t>
-  </si>
-  <si>
-    <t>ID0011223ABCD</t>
+    <t>TRX-001</t>
+  </si>
+  <si>
+    <t>XREF-001</t>
+  </si>
+  <si>
+    <t>Earn points</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -96,12 +118,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -127,16 +143,16 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -223,7 +239,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -258,7 +273,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -293,16 +307,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -424,184 +442,150 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="2"/>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="2"/>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="B10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="3"/>
-      <c r="B5" t="s">
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" t="s">
+        <v>17</v>
+      </c>
+      <c r="K10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
         <v>7</v>
       </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="E11" t="s">
         <v>10</v>
       </c>
-      <c r="G7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" t="s">
-        <v>13</v>
-      </c>
-      <c r="J7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K7" t="s">
-        <v>15</v>
-      </c>
-      <c r="L7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8">
-        <v>1000</v>
-      </c>
-      <c r="C8" s="2">
-        <v>9234234</v>
-      </c>
-      <c r="D8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8">
-        <v>7500</v>
-      </c>
-      <c r="I8" t="s">
-        <v>17</v>
-      </c>
-      <c r="L8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C9" s="2"/>
+      <c r="F11">
+        <v>100545100</v>
+      </c>
+      <c r="G11">
+        <v>7000</v>
+      </c>
+      <c r="H11" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K11" t="s">
+        <v>24</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
   </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="D10:D98" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"TRANSFER_MONEY,RECEIVE_MONEY"</formula1>
+    <dataValidation type="list" showErrorMessage="1" errorTitle="Invalid Value" error="Please select from dropdown only." sqref="E11" xr:uid="{F86DBDA5-CCA1-4A3A-BACE-A8536E9C61B6}">
+      <formula1>"PASSPORT,NID"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E10:E98" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"MOBILE_BANKING,BRANCH"</formula1>
+    <dataValidation type="list" showErrorMessage="1" errorTitle="Invalid Value" error="Please select from dropdown only." sqref="D11" xr:uid="{BACAD5C5-ADB0-4E18-8F7E-28A2444D1714}">
+      <formula1>"Mobile Banking,Branch"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>